--- a/CodeSystem-emc-custom-codes-codes.xlsx
+++ b/CodeSystem-emc-custom-codes-codes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="265">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-01-10T12:56:19+00:00</t>
+    <t>2022-01-18T13:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -400,6 +400,24 @@
   </si>
   <si>
     <t>Caregiver wants to receive SMS or other messages regarding the child's visits and health status</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE46</t>
+  </si>
+  <si>
+    <t>CommunicationRequest recipient</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE44</t>
+  </si>
+  <si>
+    <t>Person accompanying child today</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE45</t>
+  </si>
+  <si>
+    <t>Participant type Person accompanying child</t>
   </si>
   <si>
     <t>EmCare.A.DE39</t>
@@ -1097,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1741,7 +1759,7 @@
         <v>142</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47">
@@ -1749,13 +1767,13 @@
         <v>40</v>
       </c>
       <c r="B47" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="C47" t="s" s="2">
-        <v>145</v>
-      </c>
       <c r="D47" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48">
@@ -1763,13 +1781,13 @@
         <v>40</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49">
@@ -1777,13 +1795,13 @@
         <v>40</v>
       </c>
       <c r="B49" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="D49" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="D49" t="s" s="2">
-        <v>151</v>
       </c>
     </row>
     <row r="50">
@@ -1791,13 +1809,13 @@
         <v>40</v>
       </c>
       <c r="B50" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="D50" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="D50" t="s" s="2">
-        <v>154</v>
       </c>
     </row>
     <row r="51">
@@ -1805,13 +1823,13 @@
         <v>40</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="52">
@@ -1819,13 +1837,13 @@
         <v>40</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53">
@@ -1833,13 +1851,13 @@
         <v>40</v>
       </c>
       <c r="B53" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="D53" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="D53" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="54">
@@ -1847,13 +1865,13 @@
         <v>40</v>
       </c>
       <c r="B54" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="C54" t="s" s="2">
+      <c r="D54" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="D54" t="s" s="2">
-        <v>164</v>
       </c>
     </row>
     <row r="55">
@@ -1861,13 +1879,13 @@
         <v>40</v>
       </c>
       <c r="B55" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="C55" t="s" s="2">
-        <v>166</v>
-      </c>
       <c r="D55" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56">
@@ -1875,13 +1893,13 @@
         <v>40</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57">
@@ -1889,13 +1907,13 @@
         <v>40</v>
       </c>
       <c r="B57" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="D57" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="D57" t="s" s="2">
-        <v>171</v>
       </c>
     </row>
     <row r="58">
@@ -1903,10 +1921,10 @@
         <v>40</v>
       </c>
       <c r="B58" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C58" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>173</v>
@@ -2189,7 +2207,7 @@
         <v>213</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79">
@@ -2197,13 +2215,13 @@
         <v>40</v>
       </c>
       <c r="B79" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="C79" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="D79" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80">
@@ -2211,13 +2229,13 @@
         <v>40</v>
       </c>
       <c r="B80" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="C80" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="C80" t="s" s="2">
-        <v>218</v>
-      </c>
       <c r="D80" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81">
@@ -2225,13 +2243,13 @@
         <v>40</v>
       </c>
       <c r="B81" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="D81" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="D81" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="82">
@@ -2239,13 +2257,13 @@
         <v>40</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="83">
@@ -2253,13 +2271,13 @@
         <v>40</v>
       </c>
       <c r="B83" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="D83" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="D83" t="s" s="2">
-        <v>226</v>
       </c>
     </row>
     <row r="84">
@@ -2267,10 +2285,10 @@
         <v>40</v>
       </c>
       <c r="B84" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>228</v>
@@ -2301,7 +2319,7 @@
         <v>232</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="87">
@@ -2309,13 +2327,13 @@
         <v>40</v>
       </c>
       <c r="B87" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C87" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="C87" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="D87" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88">
@@ -2323,13 +2341,13 @@
         <v>40</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="89">
@@ -2337,13 +2355,13 @@
         <v>40</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90">
@@ -2351,13 +2369,13 @@
         <v>40</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C90" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="D90" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="D90" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="91">
@@ -2365,13 +2383,13 @@
         <v>40</v>
       </c>
       <c r="B91" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="C91" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="C91" t="s" s="2">
+      <c r="D91" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="D91" t="s" s="2">
-        <v>246</v>
       </c>
     </row>
     <row r="92">
@@ -2379,13 +2397,13 @@
         <v>40</v>
       </c>
       <c r="B92" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="C92" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="C92" t="s" s="2">
-        <v>248</v>
-      </c>
       <c r="D92" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="93">
@@ -2393,13 +2411,13 @@
         <v>40</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="94">
@@ -2407,13 +2425,13 @@
         <v>40</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="95">
@@ -2421,13 +2439,55 @@
         <v>40</v>
       </c>
       <c r="B95" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="D95" t="s" s="2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="C95" t="s" s="2">
+      <c r="C96" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="D95" t="s" s="2">
+      <c r="D96" t="s" s="2">
         <v>258</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="D98" t="s" s="2">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/CodeSystem-emc-custom-codes-codes.xlsx
+++ b/CodeSystem-emc-custom-codes-codes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="682">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://fhir.org/guides/who/emc-cds/CodeSystem/emc-custom-codes-codes</t>
+    <t>https://fhir.dk.swisstph-mis.ch/matchbox/fhir/CodeSystem/emc-custom-codes-codes</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-01-18T13:14:09+00:00</t>
+    <t>2022-04-21T10:41:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -144,10 +144,13 @@
     <t>Unique identification</t>
   </si>
   <si>
+    <t>Unique identifier provided or a universal ID, if used in the country</t>
+  </si>
+  <si>
     <t>EmCare.A.DE02</t>
   </si>
   <si>
-    <t>Unique Identification</t>
+    <t>Auto-generated unique identification if used by the implementation</t>
   </si>
   <si>
     <t>EmCare.A.DE03</t>
@@ -156,304 +159,1255 @@
     <t>Child's Identity unknown/prefer to remain anonymous</t>
   </si>
   <si>
+    <t>The client's identity is unknown or the client's prefers to remain anonymous</t>
+  </si>
+  <si>
     <t>EmCare.A.DE04</t>
   </si>
   <si>
     <t>First name</t>
   </si>
   <si>
+    <t>Client's first name</t>
+  </si>
+  <si>
     <t>EmCare.A.DE05</t>
   </si>
   <si>
     <t>Middle Name</t>
   </si>
   <si>
+    <t>Client's middle name</t>
+  </si>
+  <si>
     <t>EmCare.A.DE06</t>
   </si>
   <si>
     <t>Last name</t>
   </si>
   <si>
+    <t>Client's family name or last name</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE08</t>
+  </si>
+  <si>
+    <t>Date of birth</t>
+  </si>
+  <si>
+    <t>The client's date of birth (DOB), if known, OR the estimated date of birth IF not known (see EmCare.A.DE10)</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE09</t>
+  </si>
+  <si>
+    <t>Time of Birth</t>
+  </si>
+  <si>
+    <t>The client's time of birth (if &lt;1 day old)</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE10</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Age auto-calculated (presented as number of years, months, days) of the client based on date of birth OR estimated age OR based on auto-calculation from estimaged date of birth</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE11</t>
+  </si>
+  <si>
+    <t>Date of Birth not known</t>
+  </si>
+  <si>
+    <t>The client and/or Caregiver does not know the date of birth of the client (this is to check whether the age and date of birth are facts or estimations)</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE12</t>
+  </si>
+  <si>
+    <t>Provide an estimated age or estimated date of birth</t>
+  </si>
+  <si>
+    <t>The client/caregiver will provide an estimated age or estimated date of birth</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE14.1</t>
+  </si>
+  <si>
+    <t>Only know age in weeks/days/hours</t>
+  </si>
+  <si>
+    <t>The Caregiver provides the age in weeks/days/hours</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE13.1</t>
+  </si>
+  <si>
+    <t>Estimated Age</t>
+  </si>
+  <si>
+    <t>The age of the client is estimated based on information provided by the caregiver</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE15.1</t>
+  </si>
+  <si>
+    <t>Estimated Date of Birth</t>
+  </si>
+  <si>
+    <t>Estimated Date of Birth of the Client</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE16</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>The Sex of the client</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE20</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Client's home address or address that the client is consenting to disclose</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE47</t>
+  </si>
+  <si>
+    <t>Caregiver</t>
+  </si>
+  <si>
+    <t>the child could have been created from the mother therefore a relatedpersom may already exist</t>
+  </si>
+  <si>
+    <t>newCaregiver</t>
+  </si>
+  <si>
+    <t>Register a new caregiver</t>
+  </si>
+  <si>
+    <t>nan</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE21</t>
+  </si>
+  <si>
+    <t>Primary Caregiver First Name</t>
+  </si>
+  <si>
+    <t>The client's primary Caregiver's first name</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE22</t>
+  </si>
+  <si>
+    <t>Primary Caregiver Middle Name</t>
+  </si>
+  <si>
+    <t>The client's primary Caregiver's middle name</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE23</t>
+  </si>
+  <si>
+    <t>Primary Caregiver Last Name</t>
+  </si>
+  <si>
+    <t>The client's primary Caregiver's last name</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE35</t>
+  </si>
+  <si>
+    <t>Caregiver's Mobile telephone number</t>
+  </si>
+  <si>
+    <t>Client's Caregiver's mobile telephone number</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE36</t>
+  </si>
+  <si>
+    <t>Caregiver's Home telephone number</t>
+  </si>
+  <si>
+    <t>Client's Caregiver's home telephone number</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE37</t>
+  </si>
+  <si>
+    <t>Caregiver's Work telephone number</t>
+  </si>
+  <si>
+    <t>Client's Caregiver's work telephone number</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE38</t>
+  </si>
+  <si>
+    <t>Caregiver wants to receive SMS or other messages regarding the child's visits and health status</t>
+  </si>
+  <si>
+    <t>The caregiver wants to receive SMS or other messages regarding the client's contacts/visits and health status</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE46</t>
+  </si>
+  <si>
+    <t>CommunicationRequest recipient</t>
+  </si>
+  <si>
+    <t>This is needed to link the CommunicationRequest to the Caregiver</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE24</t>
+  </si>
+  <si>
+    <t>Primary Caregiver's Relationship to Client</t>
+  </si>
+  <si>
+    <t>The relationship of the primary Caregiver to the client</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE31</t>
+  </si>
+  <si>
+    <t>Biological Mother Vital Status</t>
+  </si>
+  <si>
+    <t>The client's mother and father's vital status</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE32</t>
+  </si>
+  <si>
+    <t>Biological Father Vital Status</t>
+  </si>
+  <si>
     <t>EmCare.A.DE07</t>
   </si>
   <si>
     <t>Visit date</t>
   </si>
   <si>
-    <t>EmCare.A.DE08</t>
-  </si>
-  <si>
-    <t>Date of birth</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE09</t>
-  </si>
-  <si>
-    <t>Time of Birth</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE10</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE11</t>
-  </si>
-  <si>
-    <t>Date of Birth not known</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE12</t>
-  </si>
-  <si>
-    <t>Provide an estimated age or estimated date of birth</t>
+    <t>The date and time of the client's visit</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE39</t>
+  </si>
+  <si>
+    <t>Person accompanying child today is the primary Caregiver</t>
+  </si>
+  <si>
+    <t>The client is at the visit with the primary Caregiver</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE45</t>
+  </si>
+  <si>
+    <t>Participant type Person accompanying child</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE44</t>
+  </si>
+  <si>
+    <t>Person accompanying child today</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE40</t>
+  </si>
+  <si>
+    <t>Person accompanying child today's First Name</t>
+  </si>
+  <si>
+    <t>First name of person accompanying child today when client has not arrived with the primary Caregiver</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE41</t>
+  </si>
+  <si>
+    <t>Person accompanying child today's Last Name</t>
+  </si>
+  <si>
+    <t>Last name of person accompanying child today when client has not arrived with the primary Caregiver</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE42</t>
+  </si>
+  <si>
+    <t>Person accompanying child today's contact's phone number</t>
+  </si>
+  <si>
+    <t>Phone number of the visit Caregiver</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE43</t>
+  </si>
+  <si>
+    <t>Person accompanying child today's Relationship to Client</t>
+  </si>
+  <si>
+    <t>The relationship of the visit Caregiver to the client</t>
+  </si>
+  <si>
+    <t>EmCare.B2.DE01</t>
+  </si>
+  <si>
+    <t>Type of Visit</t>
+  </si>
+  <si>
+    <t>This is the type of visit - planned or unplanned</t>
+  </si>
+  <si>
+    <t>EmCare.B3.DE01</t>
+  </si>
+  <si>
+    <t>Reason for Consultation</t>
+  </si>
+  <si>
+    <t>The reason for the client's consultation</t>
+  </si>
+  <si>
+    <t>EmCare.B3.DE05</t>
+  </si>
+  <si>
+    <t>Is the child sick today?</t>
+  </si>
+  <si>
+    <t>The client's visit is for a well child but the child is also presenting as sick</t>
+  </si>
+  <si>
+    <t>EmCare.B3.DE06</t>
+  </si>
+  <si>
+    <t>Type of Consultation</t>
+  </si>
+  <si>
+    <t>The client's visit is for a new consultation</t>
+  </si>
+  <si>
+    <t>EmCare.B3.DE09</t>
+  </si>
+  <si>
+    <t>Referred by a Health Care Worker or Health Care Facility</t>
+  </si>
+  <si>
+    <t>The client was referred by a Health Care Worker in the community or another Health Care Facility</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE01</t>
+  </si>
+  <si>
+    <t>Auxiliary Temperature</t>
+  </si>
+  <si>
+    <t>The client's axillary temperature in degrees Celsius (temperature taken under the armpit)</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE02</t>
+  </si>
+  <si>
+    <t>Prefer to take Rectal Temperature</t>
+  </si>
+  <si>
+    <t>The health care worker prefers to take the client's rectal temperature</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE03</t>
+  </si>
+  <si>
+    <t>Rectal Temperature</t>
+  </si>
+  <si>
+    <t>The client's rectal temperature in degrees Celsius (temperature taken in the rectum)</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE04</t>
+  </si>
+  <si>
+    <t>Thermometer not available</t>
+  </si>
+  <si>
+    <t>A thermometer is not available to accurately measure the client's temperature</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE05</t>
+  </si>
+  <si>
+    <t>Hot to Touch</t>
+  </si>
+  <si>
+    <t>The client is hot to touch</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE06</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>The client's weight in Kilograms</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE07</t>
+  </si>
+  <si>
+    <t>Weight cannot be measured</t>
+  </si>
+  <si>
+    <t>The client's weight cannot be measured</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE08</t>
+  </si>
+  <si>
+    <t>Estimated Weight</t>
+  </si>
+  <si>
+    <t>The client's weight has been estimated - to be used for treatment dosing only</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE09</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>The client's height in Centimeters</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE10</t>
+  </si>
+  <si>
+    <t>Prefer to measure length</t>
+  </si>
+  <si>
+    <t>The health care worker would prefer to measure the client using length</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE11</t>
+  </si>
+  <si>
+    <t>Height cannot be measured</t>
+  </si>
+  <si>
+    <t>The client's height cannot be measured</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE12</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>The client's length in Centimeters</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE13</t>
+  </si>
+  <si>
+    <t>Length cannot be measured</t>
+  </si>
+  <si>
+    <t>The client's length cannot be measured</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE14</t>
+  </si>
+  <si>
+    <t>Weight for Height (WFH) Z Scores</t>
+  </si>
+  <si>
+    <t>The client's weight for height Z Score</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE15</t>
+  </si>
+  <si>
+    <t>Weight for Length (WFL) Z Scores</t>
+  </si>
+  <si>
+    <t>The client's weight for length Z Score</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE16</t>
+  </si>
+  <si>
+    <t>Weight for Age (WFA) Z Scores</t>
+  </si>
+  <si>
+    <t>The client's weight for age z score</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE17</t>
+  </si>
+  <si>
+    <t>MUAC (Mid Upper Arm Circumference)</t>
+  </si>
+  <si>
+    <t>The client's Mid Upper Arm Circumference in Millimeters (child ≥6 months old)</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE18</t>
+  </si>
+  <si>
+    <t>Visually assess for whether underweight (for drug dose calculation)</t>
+  </si>
+  <si>
+    <t>The health care worker visually assesses for whether underweight (for drug dosing calculations)</t>
+  </si>
+  <si>
+    <t>EmCare.B6.DE22</t>
+  </si>
+  <si>
+    <t>Date of measurement</t>
+  </si>
+  <si>
+    <t>The date when the measurement was taken</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE01</t>
+  </si>
+  <si>
+    <t>Obstructed or Absent Breathing</t>
+  </si>
+  <si>
+    <t>The client has obstructed or absent breathing</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE02</t>
+  </si>
+  <si>
+    <t>Convulsing Now</t>
+  </si>
+  <si>
+    <t>The client is convulsing now</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE03</t>
+  </si>
+  <si>
+    <t>Convulsion(s) in this Illness</t>
+  </si>
+  <si>
+    <t>The client is reported to have had one or more convulsions</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE04</t>
+  </si>
+  <si>
+    <t>Number of convulsions in this illness</t>
+  </si>
+  <si>
+    <t>The number of convulsion(s) the client is reported to have had in this illness</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE08</t>
+  </si>
+  <si>
+    <t>Unconscious or Lethargic</t>
+  </si>
+  <si>
+    <t>The client is unconscious or lethargic</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE09</t>
+  </si>
+  <si>
+    <t>Not able to drink or breastfeed</t>
+  </si>
+  <si>
+    <t>The client has reported not to have been able to drink or breastfeed or currently is not able to drink or breastfeed.</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE10</t>
+  </si>
+  <si>
+    <t>Vomiting</t>
+  </si>
+  <si>
+    <t>The client is reported to be vomiting everything or vomiting but not everything or no vomiting</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE14</t>
+  </si>
+  <si>
+    <t>Oral Fluid Test</t>
+  </si>
+  <si>
+    <t>The healthcare worker or care giver  offers the client fluid to check if the client can drink and to check reactions (oral fluid test)</t>
+  </si>
+  <si>
+    <t>EmCare.B8/B9.DE01</t>
+  </si>
+  <si>
+    <t>EmCare.B8/B9.DE02</t>
+  </si>
+  <si>
+    <t>EmCare.B10S1.DE05</t>
+  </si>
+  <si>
+    <t>Cough</t>
+  </si>
+  <si>
+    <t>The client is reported to have or has had a cough</t>
+  </si>
+  <si>
+    <t>EmCare.B10S1.DE06</t>
+  </si>
+  <si>
+    <t>Cough for how long?</t>
+  </si>
+  <si>
+    <t>Length of time the client is reported to have or has had the cough</t>
+  </si>
+  <si>
+    <t>EmCare.B10S1.DE01</t>
+  </si>
+  <si>
+    <t>Difficulty Breathing</t>
+  </si>
+  <si>
+    <t>The client is reported to have or has had difficulty breathing</t>
+  </si>
+  <si>
+    <t>EmCare.B10S1.DE02</t>
+  </si>
+  <si>
+    <t>Difficulty breathing for how long?</t>
+  </si>
+  <si>
+    <t>The length of time the client has or has had difficulty breathing</t>
+  </si>
+  <si>
+    <t>EmCare.B11S1.DE01</t>
+  </si>
+  <si>
+    <t>Diarrhoea</t>
+  </si>
+  <si>
+    <t>The client is reported to have or has had diarrhoea</t>
+  </si>
+  <si>
+    <t>EmCare.B11S1.DE02</t>
+  </si>
+  <si>
+    <t>Diarrhoea for how long?</t>
+  </si>
+  <si>
+    <t>The length of time the client is reported to have or has had diarrhoea</t>
+  </si>
+  <si>
+    <t>EmCare.B11S1.DE05</t>
+  </si>
+  <si>
+    <t>Blood in the stool in this Illness</t>
+  </si>
+  <si>
+    <t>The client is reported to have or has had blood in the stool in this Illness</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE02</t>
+  </si>
+  <si>
+    <t>Fever</t>
+  </si>
+  <si>
+    <t>The client is reported to have or has had fever</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE03</t>
+  </si>
+  <si>
+    <t>Fever for how long?</t>
+  </si>
+  <si>
+    <t>The length of time the client has or has had fever</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE06</t>
+  </si>
+  <si>
+    <t>Has Fever been present every day since the Fever started?</t>
+  </si>
+  <si>
+    <t>The client has had fever present every day since the fever started</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE07</t>
+  </si>
+  <si>
+    <t>Refusal to Use a Limb</t>
+  </si>
+  <si>
+    <t>The client is reported to be refusing to use a limb</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE08</t>
+  </si>
+  <si>
+    <t>Pain</t>
+  </si>
+  <si>
+    <t>The client is reported to have,  has had, or appears to be in pain</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE13</t>
+  </si>
+  <si>
+    <t>Malaria Risk</t>
+  </si>
+  <si>
+    <t>The client is in a high / low / no malaria risk area</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE17</t>
+  </si>
+  <si>
+    <t>Recent Travel to a High Malaria Risk area</t>
+  </si>
+  <si>
+    <t>The client has recently travelled to a high Malaria risk area</t>
+  </si>
+  <si>
+    <t>EmCare.B13S1.DE01</t>
+  </si>
+  <si>
+    <t>Ear problem</t>
+  </si>
+  <si>
+    <t>The client is reported to have had or has an ear problem</t>
+  </si>
+  <si>
+    <t>EmCare.B13S1.DE02</t>
+  </si>
+  <si>
+    <t>Ear pain</t>
+  </si>
+  <si>
+    <t>The client is reported to have had or has ear pain</t>
+  </si>
+  <si>
+    <t>EmCare.B13S1.DE03</t>
+  </si>
+  <si>
+    <t>Ear discharge</t>
+  </si>
+  <si>
+    <t>The client is reported to have or has had ear discharge</t>
+  </si>
+  <si>
+    <t>EmCare.B13S1.DE04</t>
+  </si>
+  <si>
+    <t>Ear discharge for how long?</t>
+  </si>
+  <si>
+    <t>The length of time client has or has had ear discharge</t>
+  </si>
+  <si>
+    <t>EmCare.B14S1.DE03</t>
+  </si>
+  <si>
+    <t>Eye Problem</t>
+  </si>
+  <si>
+    <t>The client is reported to have an eye problem</t>
+  </si>
+  <si>
+    <t>EmCare.B14S1.DE01</t>
+  </si>
+  <si>
+    <t>Skin Problem</t>
+  </si>
+  <si>
+    <t>The client is reported to have or has had a skin problem</t>
+  </si>
+  <si>
+    <t>EmCare.B14S1.DE02</t>
+  </si>
+  <si>
+    <t>Itchy Skin</t>
+  </si>
+  <si>
+    <t>The client is reported to have itchy skin</t>
+  </si>
+  <si>
+    <t>EmCare.B10S2.DE01</t>
+  </si>
+  <si>
+    <t>Respiratory Rate</t>
+  </si>
+  <si>
+    <t>The client's respiratory rate</t>
+  </si>
+  <si>
+    <t>EmCare.B10S2.DE03</t>
+  </si>
+  <si>
+    <t>Chest Indrawing</t>
+  </si>
+  <si>
+    <t>The client has chest indrawing</t>
+  </si>
+  <si>
+    <t>EmCare.B10S2.DE04</t>
+  </si>
+  <si>
+    <t>The client has been HIV exposed / infected</t>
+  </si>
+  <si>
+    <t>EmCare.B10S2.DE05</t>
+  </si>
+  <si>
+    <t>Stridor in a calm child</t>
+  </si>
+  <si>
+    <t>The client has stridor in a calm child while the client is at rest</t>
+  </si>
+  <si>
+    <t>EmCare.B10S2.DE06</t>
+  </si>
+  <si>
+    <t>Wheezing</t>
+  </si>
+  <si>
+    <t>The client is wheezing</t>
+  </si>
+  <si>
+    <t>EmCare.B10S2.DE07</t>
+  </si>
+  <si>
+    <t>Recurrent Wheeze</t>
+  </si>
+  <si>
+    <t>The client has experienced recurrent wheeze</t>
+  </si>
+  <si>
+    <t>EmCare.B10S2.DE08</t>
+  </si>
+  <si>
+    <t>Oxygen Saturation</t>
+  </si>
+  <si>
+    <t>The client's oxygen saturation measurement</t>
+  </si>
+  <si>
+    <t>EmCare.B11S2.DE01</t>
+  </si>
+  <si>
+    <t>Sunken eyes</t>
+  </si>
+  <si>
+    <t>The client has sunken eyes</t>
+  </si>
+  <si>
+    <t>EmCare.B11S2.DE02</t>
+  </si>
+  <si>
+    <t>Skin pinch of Abdomen</t>
+  </si>
+  <si>
+    <t>The healthcare worker pinches the skin of the client's abdomen for 1 second and then observes how long the skin takes to return to normal once released</t>
+  </si>
+  <si>
+    <t>EmCare.B11S2.DE06</t>
+  </si>
+  <si>
+    <t>Restless and Irritable</t>
+  </si>
+  <si>
+    <t>The client is restless and irritable</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE01</t>
+  </si>
+  <si>
+    <t>Stiff neck</t>
+  </si>
+  <si>
+    <t>The client has a stiff neck</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE02</t>
+  </si>
+  <si>
+    <t>Refusal to use a limb</t>
+  </si>
+  <si>
+    <t>The health care worker has seen that  client is refusing to use a limb</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE03</t>
+  </si>
+  <si>
+    <t>Warm Tender or Swollen Joint or Bone</t>
+  </si>
+  <si>
+    <t>The client has a warm tender or swollen joint or bone</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE04</t>
+  </si>
+  <si>
+    <t>Oral Sores or Mouth Ulcers</t>
+  </si>
+  <si>
+    <t>The client is reported to have oral sores or mouth ulcers</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE05</t>
+  </si>
+  <si>
+    <t>Obvious Cause of Fever (to determine if Malaria test required)</t>
+  </si>
+  <si>
+    <t>The health care worker determines if there is an obvious cause of fever (to determine if Malaria test is required)  If no obvious cause of fever a malaria test will be prompted</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE06</t>
+  </si>
+  <si>
+    <t>Runny nose</t>
+  </si>
+  <si>
+    <t>The client has a runny nose</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE07</t>
+  </si>
+  <si>
+    <t>Red eyes</t>
+  </si>
+  <si>
+    <t>The client has red eyes</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE08</t>
+  </si>
+  <si>
+    <t>Generalised rash</t>
+  </si>
+  <si>
+    <t>The client has a generalised rash</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE09</t>
+  </si>
+  <si>
+    <t>Measles Rash</t>
+  </si>
+  <si>
+    <t>The client has a measles rash</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE10</t>
+  </si>
+  <si>
+    <t>Measles within the last 3 months</t>
+  </si>
+  <si>
+    <t>The client has had measles in the last 3 months</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE11</t>
+  </si>
+  <si>
+    <t>Clouding of the Cornea</t>
+  </si>
+  <si>
+    <t>The client has clouding of the cornea</t>
+  </si>
+  <si>
+    <t>EmCare.B12S2.DE12</t>
+  </si>
+  <si>
+    <t>Pus Draining from Eye</t>
+  </si>
+  <si>
+    <t>The client has pus draining from the eye</t>
+  </si>
+  <si>
+    <t>EmCare.B13S2.DE01</t>
+  </si>
+  <si>
+    <t>Tender swelling behind the ear</t>
+  </si>
+  <si>
+    <t>The client has tender swelling behind the ear</t>
+  </si>
+  <si>
+    <t>EmCare.B13S2.DE02</t>
+  </si>
+  <si>
+    <t>Pus Seen Draining from the Ear</t>
+  </si>
+  <si>
+    <t>The client has pus draining from the ear which has been seen by the health care worker</t>
+  </si>
+  <si>
+    <t>EmCare.B13S2.DE03</t>
+  </si>
+  <si>
+    <t>Pus Seen Draining from the Ear for how long</t>
+  </si>
+  <si>
+    <t>The length of time the client has or has had pus draining from the ear</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE01</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE02</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE03</t>
+  </si>
+  <si>
+    <t>Is Clouding of Cornea a new problem</t>
+  </si>
+  <si>
+    <t>Clouding of the cornea in the client is a new problem</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE04</t>
+  </si>
+  <si>
+    <t>Has Clouding of Cornea previously been treated</t>
+  </si>
+  <si>
+    <t>Clouding of the cornea has not been previously treated in the client</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE05</t>
+  </si>
+  <si>
+    <t>Generalised or Localised Skin Problem</t>
+  </si>
+  <si>
+    <t>The client has a generalised or localised skin problem</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE08</t>
+  </si>
+  <si>
+    <t>Blisters, Sores or Pustules</t>
+  </si>
+  <si>
+    <t>The client has blisters, sores or pustules</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE09</t>
+  </si>
+  <si>
+    <t>Type of Skin Problem</t>
+  </si>
+  <si>
+    <t>The client has a specific type of skin problem(s)</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE18</t>
+  </si>
+  <si>
+    <t>Signs of Severe Impetigo / Folliculitis</t>
+  </si>
+  <si>
+    <t>The client has signs of Severe Impetigo / Folliculitis</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE29</t>
+  </si>
+  <si>
+    <t>Extensive and Severe Ringworm</t>
+  </si>
+  <si>
+    <t>The client has an extensive skin problem</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE30</t>
+  </si>
+  <si>
+    <t>Severe Seborrhea</t>
+  </si>
+  <si>
+    <t>The client has a severe skin problem</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE31</t>
+  </si>
+  <si>
+    <t>Oral sores or Mouth Ulcers</t>
+  </si>
+  <si>
+    <t>The client has oral sores or mouth ulcers</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE35</t>
+  </si>
+  <si>
+    <t>Add a Skin or Mouth or Eye Problem</t>
+  </si>
+  <si>
+    <t>The health care worker would like to add a Skin or Mouth or Eye problem found during the physical exam</t>
+  </si>
+  <si>
+    <t>EmCare.B15S2.DE02</t>
+  </si>
+  <si>
+    <t>Severe Palmar Pallor</t>
+  </si>
+  <si>
+    <t>The client has severe palmar pallor</t>
+  </si>
+  <si>
+    <t>EmCare.B15S2.DE05</t>
+  </si>
+  <si>
+    <t>EmCare.B16S2.DE01</t>
+  </si>
+  <si>
+    <t>Oedema of both feet</t>
+  </si>
+  <si>
+    <t>The client has oedema of both feet</t>
+  </si>
+  <si>
+    <t>Universal ID</t>
+  </si>
+  <si>
+    <t>Auto-generated ID</t>
+  </si>
+  <si>
+    <t>Unknown ID</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE17</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>The client is Female</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE18</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>The client is Male</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE19</t>
+  </si>
+  <si>
+    <t>Not Specified</t>
+  </si>
+  <si>
+    <t>The client's sex is not specified</t>
   </si>
   <si>
     <t>EmCare.A.DE13</t>
   </si>
   <si>
-    <t>Estimated Age</t>
-  </si>
-  <si>
-    <t>Provide an estimated age or estimated date of birth - Estimated Age</t>
+    <t>The age of the client is estimated based on physical evidence</t>
   </si>
   <si>
     <t>EmCare.A.DE14</t>
   </si>
   <si>
-    <t>Only know age in weeks/days/hours</t>
-  </si>
-  <si>
-    <t>Provide an estimated age or estimated date of birth - Only know age in weeks/days/hours</t>
-  </si>
-  <si>
     <t>EmCare.A.DE15</t>
   </si>
   <si>
-    <t>Estimated Date of Birth</t>
-  </si>
-  <si>
-    <t>Provide an estimated age or estimated date of birth - Estimated Date of Birth</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE16</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>female</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Sex - Female</t>
-  </si>
-  <si>
-    <t>male</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Sex - Male</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>Not Specified</t>
-  </si>
-  <si>
-    <t>Sex - Not Specified</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE20</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE21</t>
-  </si>
-  <si>
-    <t>Primary Caregiver First Name</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE22</t>
-  </si>
-  <si>
-    <t>Primary Caregiver Middle Name</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE23</t>
-  </si>
-  <si>
-    <t>Primary Caregiver Last Name</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE24</t>
-  </si>
-  <si>
-    <t>Primary Caregiver's Relationship to Client</t>
-  </si>
-  <si>
-    <t>MTH</t>
+    <t>EmCare.A.DE25</t>
   </si>
   <si>
     <t>Mother</t>
   </si>
   <si>
-    <t>Primary Caregiver's Relationship to Client - Mother</t>
-  </si>
-  <si>
-    <t>FTH</t>
+    <t>The Caregiver is the client's mother</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE26</t>
   </si>
   <si>
     <t>Father</t>
   </si>
   <si>
-    <t>Primary Caregiver's Relationship to Client - Father</t>
-  </si>
-  <si>
-    <t>CHILD</t>
+    <t>The Caregiver is the client's father</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE27</t>
   </si>
   <si>
     <t>Sibling</t>
   </si>
   <si>
-    <t>Primary Caregiver's Relationship to Client - Sibling</t>
-  </si>
-  <si>
-    <t>EXT</t>
+    <t>The Caregiver is the client's sibling</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE28</t>
   </si>
   <si>
     <t>Extended family</t>
   </si>
   <si>
-    <t>Primary Caregiver's Relationship to Client - Extended family</t>
-  </si>
-  <si>
-    <t>PRNFOST</t>
+    <t>The Caregiver is the client's extended family</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE29</t>
   </si>
   <si>
     <t>Legal Guardian</t>
   </si>
   <si>
-    <t>Primary Caregiver's Relationship to Client - Legal Guardian</t>
-  </si>
-  <si>
-    <t>FRND</t>
+    <t>The Caregiver is the client's legal guardian</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE30</t>
   </si>
   <si>
     <t>Not Related</t>
   </si>
   <si>
-    <t>Primary Caregiver's Relationship to Client - Not Related</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE31</t>
-  </si>
-  <si>
-    <t>Biological Mother Vital Status</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE32</t>
-  </si>
-  <si>
-    <t>Biological Father Vital Status</t>
+    <t>The Caregiver is not related to the client</t>
   </si>
   <si>
     <t>EmCare.A.DE33</t>
   </si>
   <si>
-    <t>Relationship Mother</t>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Biological Mother or Father Vital Status unknown</t>
   </si>
   <si>
     <t>EmCare.A.DE34</t>
   </si>
   <si>
-    <t>Relationship Father</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE35</t>
-  </si>
-  <si>
-    <t>Caregiver's Mobile telephone number</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE36</t>
-  </si>
-  <si>
-    <t>Caregiver's Home telephone number</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE37</t>
-  </si>
-  <si>
-    <t>Caregiver's Work telephone number</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE38</t>
-  </si>
-  <si>
-    <t>Caregiver wants to receive SMS or other messages regarding the child's visits and health status</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE46</t>
-  </si>
-  <si>
-    <t>CommunicationRequest recipient</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE44</t>
-  </si>
-  <si>
-    <t>Person accompanying child today</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE45</t>
-  </si>
-  <si>
-    <t>Participant type Person accompanying child</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE39</t>
-  </si>
-  <si>
-    <t>Person accompanying child today is same as the primary Caregiver</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE40</t>
-  </si>
-  <si>
-    <t>Person accompanying child today's First Name</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE41</t>
-  </si>
-  <si>
-    <t>Person accompanying child today's Last Name</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE42</t>
-  </si>
-  <si>
-    <t>Person accompanying child today's contact's phone number</t>
-  </si>
-  <si>
-    <t>EmCare.A.DE43</t>
-  </si>
-  <si>
-    <t>Person accompanying child today's Relationship to Client</t>
-  </si>
-  <si>
-    <t>EmCare.B2.DE01</t>
-  </si>
-  <si>
-    <t>Type of Visit</t>
+    <t>Alive</t>
+  </si>
+  <si>
+    <t>Biological Mother or Father Alive</t>
+  </si>
+  <si>
+    <t>Dead</t>
+  </si>
+  <si>
+    <t>Biological Mother or Father dead</t>
+  </si>
+  <si>
+    <t>SMS</t>
   </si>
   <si>
     <t>EmCare.B2.DE02</t>
@@ -462,7 +1416,7 @@
     <t>Planned</t>
   </si>
   <si>
-    <t>Type of Visit - Planned</t>
+    <t>The visit is planned</t>
   </si>
   <si>
     <t>EmCare.B2.DE03</t>
@@ -471,13 +1425,7 @@
     <t>Unplanned</t>
   </si>
   <si>
-    <t>Type of Visit - Unplanned</t>
-  </si>
-  <si>
-    <t>EmCare.B3.DE01</t>
-  </si>
-  <si>
-    <t>Reason for Consultation</t>
+    <t>The visit is unplanned</t>
   </si>
   <si>
     <t>EmCare.B3.DE02</t>
@@ -486,7 +1434,7 @@
     <t>Life Threatening Emergency</t>
   </si>
   <si>
-    <t>Reason for Consultation - Life Threatening Emergency</t>
+    <t>The client had a life threatening emergency</t>
   </si>
   <si>
     <t>EmCare.B3.DE03</t>
@@ -495,7 +1443,7 @@
     <t>Sick Child</t>
   </si>
   <si>
-    <t>Reason for Consultation - Sick Child</t>
+    <t>The client's visit is for a sick child consultation</t>
   </si>
   <si>
     <t>EmCare.B3.DE04</t>
@@ -504,19 +1452,19 @@
     <t>Well Child</t>
   </si>
   <si>
-    <t>Reason for Consultation - Well Child</t>
-  </si>
-  <si>
-    <t>EmCare.B3.DE05</t>
-  </si>
-  <si>
-    <t>Is the child sick today</t>
-  </si>
-  <si>
-    <t>EmCare.B3.DE06</t>
-  </si>
-  <si>
-    <t>Type of Consultation</t>
+    <t>The client's visit is for a well child consultation</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>EmCare.B3.DE07</t>
@@ -525,289 +1473,592 @@
     <t>New Consultation</t>
   </si>
   <si>
-    <t>Type of Consultation - New Consultation</t>
-  </si>
-  <si>
     <t>EmCare.B3.DE08</t>
   </si>
   <si>
     <t>Follow Up</t>
   </si>
   <si>
-    <t>Type of Consultation - Follow Up</t>
-  </si>
-  <si>
-    <t>EmCare.B3.DE09</t>
-  </si>
-  <si>
-    <t>Referred by a Health Care Worker or Health Care Facility</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE01</t>
-  </si>
-  <si>
-    <t>Axillary Temperature</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE02</t>
-  </si>
-  <si>
-    <t>Prefer to take Rectal Temperature</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE03</t>
-  </si>
-  <si>
-    <t>Rectal Temperature</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE04</t>
-  </si>
-  <si>
-    <t>Thermometer not available</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE05</t>
-  </si>
-  <si>
-    <t>Hot to Touch</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE06</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE07</t>
-  </si>
-  <si>
-    <t>Weight cannot be measured</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE08</t>
-  </si>
-  <si>
-    <t>Estimated Weight</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE09</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE10</t>
-  </si>
-  <si>
-    <t>Prefer to measure length</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE11</t>
-  </si>
-  <si>
-    <t>Height cannot be measured</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE12</t>
-  </si>
-  <si>
-    <t>Length</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE13</t>
-  </si>
-  <si>
-    <t>Length cannot be measured</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE14</t>
-  </si>
-  <si>
-    <t>Weight for Height (WFH) Z Scores</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE15</t>
-  </si>
-  <si>
-    <t>Weight for Length (WFL) Z Scores</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE16</t>
-  </si>
-  <si>
-    <t>Weight for Age (WFA) Z Scores</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE17</t>
-  </si>
-  <si>
-    <t>MUAC (Mid Upper Arm Circumference)</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE18</t>
-  </si>
-  <si>
-    <t>Visually assess for whether underweight (for drug dose calculation)</t>
-  </si>
-  <si>
-    <t>EmCare.B6.DE22</t>
-  </si>
-  <si>
-    <t>Date of measurement</t>
-  </si>
-  <si>
-    <t>EmCare.B7.DE01</t>
-  </si>
-  <si>
-    <t>Obstructed or Absent Breathing</t>
-  </si>
-  <si>
-    <t>EmCare.B7.DE02</t>
-  </si>
-  <si>
-    <t>Convulsing Now</t>
-  </si>
-  <si>
-    <t>EmCare.B7.DE03</t>
-  </si>
-  <si>
-    <t>Convulsion(s) in this Illness</t>
-  </si>
-  <si>
-    <t>Convulsing Now - Convulsion(s) in this Illness</t>
-  </si>
-  <si>
-    <t>EmCare.B7.DE04</t>
-  </si>
-  <si>
-    <t>Number of convulsions in this illness</t>
-  </si>
-  <si>
-    <t>one</t>
+    <t>The client's visit is for a follow up consultation</t>
+  </si>
+  <si>
+    <t>EmCare.B10S1.DE07</t>
+  </si>
+  <si>
+    <t>Less than 14 days</t>
+  </si>
+  <si>
+    <t>The client has had a cough for less than 14 days</t>
+  </si>
+  <si>
+    <t>EmCare.B10S1.DE08</t>
+  </si>
+  <si>
+    <t>14 days or More</t>
+  </si>
+  <si>
+    <t>The client has had a cough for 14 days or more</t>
+  </si>
+  <si>
+    <t>EmCare.B10S1.DE03</t>
+  </si>
+  <si>
+    <t>The client has had difficulty breathing for less than 14 days</t>
+  </si>
+  <si>
+    <t>EmCare.B10S1.DE04</t>
+  </si>
+  <si>
+    <t>The client has had difficulty breathing for 14 days or more</t>
+  </si>
+  <si>
+    <t>EmCare.B11S1.DE03</t>
+  </si>
+  <si>
+    <t>The client has had diarrhoea for less than 14 days</t>
+  </si>
+  <si>
+    <t>EmCare.B11S1.DE04</t>
+  </si>
+  <si>
+    <t>The client has had diarrhoea for 14 days or more</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE04</t>
+  </si>
+  <si>
+    <t>Less than 7 days</t>
+  </si>
+  <si>
+    <t>The client has had fever for less than 7 days</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE05</t>
+  </si>
+  <si>
+    <t>7 Days or more</t>
+  </si>
+  <si>
+    <t>The client has had fever for 7 days or more</t>
+  </si>
+  <si>
+    <t>joint_pain</t>
+  </si>
+  <si>
+    <t>Joint or Bone Pain</t>
+  </si>
+  <si>
+    <t>The client is reported to have or has had joint or bone pain</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE09</t>
+  </si>
+  <si>
+    <t>Pain or Difficulty Passing Urine or Crying when Passing Urine</t>
+  </si>
+  <si>
+    <t>The client is reported to have or has had pain or difficulty passing urine or crying when passing urine</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE10</t>
+  </si>
+  <si>
+    <t>The client is reported to have or is observed to have skin pain or problem</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE11</t>
+  </si>
+  <si>
+    <t>Ear Pain</t>
+  </si>
+  <si>
+    <t>The client is reported to have or has had ear pain</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE12</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>The client is reported to have or has had another type of pain</t>
+  </si>
+  <si>
+    <t>no_pain</t>
+  </si>
+  <si>
+    <t>No Pain</t>
+  </si>
+  <si>
+    <t>The client is reported to have no pain</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE14</t>
+  </si>
+  <si>
+    <t>High Malaria Risk</t>
+  </si>
+  <si>
+    <t>The client is in a high malaria risk area</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE15</t>
+  </si>
+  <si>
+    <t>Low Malaria Risk</t>
+  </si>
+  <si>
+    <t>The client is in a low malaria risk area</t>
+  </si>
+  <si>
+    <t>EmCare.B12S1.DE16</t>
+  </si>
+  <si>
+    <t>No Malaria Risk</t>
+  </si>
+  <si>
+    <t>The client is in a no malaria risk area</t>
+  </si>
+  <si>
+    <t>EmCare.B13S1.DE05</t>
+  </si>
+  <si>
+    <t>The client has had ear discharge for less than 14 days</t>
+  </si>
+  <si>
+    <t>EmCare.B13S1.DE06</t>
+  </si>
+  <si>
+    <t>14 days or more</t>
+  </si>
+  <si>
+    <t>The client has had ear discharge for 14 days or more</t>
+  </si>
+  <si>
+    <t>oxygen_saturation_above_90</t>
+  </si>
+  <si>
+    <t>Oxygen Saturation &gt;= 90 %</t>
+  </si>
+  <si>
+    <t>The client's oxygen saturation is more than or equal to 90 %</t>
+  </si>
+  <si>
+    <t>EmCare.B10S2.DE09</t>
+  </si>
+  <si>
+    <t>Oxygen Saturation &lt; 90 %</t>
+  </si>
+  <si>
+    <t>The client's oxygen saturation is less than 90 %</t>
+  </si>
+  <si>
+    <t>EmCare.B10S2.DE10</t>
+  </si>
+  <si>
+    <t>Oxygen saturation not measured</t>
+  </si>
+  <si>
+    <t>The clients oxygen saturation was not measured</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE05</t>
   </si>
   <si>
     <t>One Convulsion</t>
   </si>
   <si>
-    <t>Number of convulsions in this illness - One Convulsion</t>
-  </si>
-  <si>
-    <t>multiple</t>
+    <t>The client is reported to have had one convulsion in this illness</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE06</t>
   </si>
   <si>
     <t>Two or more convulsions</t>
   </si>
   <si>
-    <t>Number of convulsions in this illness - Two or more convulsions</t>
-  </si>
-  <si>
-    <t>EmCare.B7.DE07</t>
-  </si>
-  <si>
-    <t>Convulsion(s) last 15 minutes or more</t>
-  </si>
-  <si>
-    <t>EmCare.B7.DE08</t>
-  </si>
-  <si>
-    <t>Unconscious or Lethargic</t>
-  </si>
-  <si>
-    <t>EmCare.B7.DE09</t>
-  </si>
-  <si>
-    <t>Not able to drink or breastfeed</t>
-  </si>
-  <si>
-    <t>EmCare.B7.DE10</t>
-  </si>
-  <si>
-    <t>Vomiting</t>
-  </si>
-  <si>
-    <t>everything</t>
+    <t>The client is reported to have had two or more convulsions in this illness</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE11</t>
   </si>
   <si>
     <t>Vomiting Everything</t>
   </si>
   <si>
-    <t>Vomiting - Vomiting Everything</t>
-  </si>
-  <si>
-    <t>not-everything</t>
+    <t>The client is reported to be vomiting everything</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE12</t>
   </si>
   <si>
     <t>Vomiting but Not Everything</t>
   </si>
   <si>
-    <t>Vomiting - Vomiting but Not Everything</t>
-  </si>
-  <si>
-    <t>nothing</t>
-  </si>
-  <si>
-    <t>No Vomiting</t>
-  </si>
-  <si>
-    <t>Vomiting - No Vomiting</t>
-  </si>
-  <si>
-    <t>EmCare.B7.DE14</t>
-  </si>
-  <si>
-    <t>Oral Fluid Test</t>
+    <t>The client is reported to be vomiting but not vomiting everything</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE15</t>
   </si>
   <si>
     <t>Vomits immediately / everything</t>
   </si>
   <si>
-    <t>Oral Fluid Test - Vomits immediately / everything</t>
-  </si>
-  <si>
-    <t>unable</t>
+    <t>The client vomits immediately / everything</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE16</t>
   </si>
   <si>
     <t>Completely unable to drink</t>
   </si>
   <si>
-    <t>Oral Fluid Test - Completely unable to drink</t>
-  </si>
-  <si>
-    <t>poorly</t>
+    <t>The client is completely unable to drink</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE17</t>
   </si>
   <si>
     <t>Drinks poorly</t>
   </si>
   <si>
-    <t>Oral Fluid Test - Drinks poorly</t>
-  </si>
-  <si>
-    <t>thirstily</t>
+    <t>The client drinks poorly</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE18</t>
   </si>
   <si>
     <t>Drinks eagerly / thirstily</t>
   </si>
   <si>
-    <t>Oral Fluid Test - Drinks eagerly / thirstily</t>
-  </si>
-  <si>
-    <t>normally</t>
+    <t>The client drinks eagerly / thirstily</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE19</t>
   </si>
   <si>
     <t>Drinks normally</t>
   </si>
   <si>
-    <t>Oral Fluid Test - Drinks normally</t>
-  </si>
-  <si>
-    <t>no-test</t>
+    <t>The client drinks normally</t>
+  </si>
+  <si>
+    <t>EmCare.B7.DE20</t>
   </si>
   <si>
     <t>Unable to perform test - assumes vomits everything/unable to drink</t>
   </si>
   <si>
-    <t>Oral Fluid Test - Unable to perform test - assumes vomits everything/unable to drink</t>
+    <t>The health care worker is unable to perform test on the client therefore the health care worker should assume the client vomits everything or is unable to drink</t>
+  </si>
+  <si>
+    <t>fluid_test_passed</t>
+  </si>
+  <si>
+    <t>Successful</t>
+  </si>
+  <si>
+    <t>The client passes the fluid test</t>
+  </si>
+  <si>
+    <t>EmCare.B11S2.DE03</t>
+  </si>
+  <si>
+    <t>Skin Pinch Goes back Very slowly (More than 2 seconds)</t>
+  </si>
+  <si>
+    <t>The client's skin goes back very slowly after skin pinch of abdomen (More than 2 seconds)</t>
+  </si>
+  <si>
+    <t>EmCare.B11S2.DE04</t>
+  </si>
+  <si>
+    <t>Skin Pinch Goes back Slowly (2 seconds or fewer, but not immediately)</t>
+  </si>
+  <si>
+    <t>The client's skin goes back slowly after skin pinch of abdomen (2 seconds or fewer, but not immediately)</t>
+  </si>
+  <si>
+    <t>EmCare.B11S2.DE05</t>
+  </si>
+  <si>
+    <t>Goes back Normally (immediately)</t>
+  </si>
+  <si>
+    <t>The client's skin goes back normally after skin pinch of abdomen (immediately)</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE19</t>
+  </si>
+  <si>
+    <t>Skin Lesions ≥ 4 cm</t>
+  </si>
+  <si>
+    <t>The client has Skin Lesions ≥ 4 cm</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE20</t>
+  </si>
+  <si>
+    <t>Red Skin Streaks</t>
+  </si>
+  <si>
+    <t>The client has red skin streaks</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE21</t>
+  </si>
+  <si>
+    <t>Tender Nodes (Nodules) under the skin</t>
+  </si>
+  <si>
+    <t>The client has tender nodes (nodules) under the skin that can appear on any part of the face or body</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE22</t>
+  </si>
+  <si>
+    <t>Skin Infection extends to Muscle</t>
+  </si>
+  <si>
+    <t>The client has skin infection that extends to muscle</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE23</t>
+  </si>
+  <si>
+    <t>Molluscum Contagiosum - Skin coloured pearly white papules with central umbilication. Most commonly seen on face and trunk in children.</t>
+  </si>
+  <si>
+    <t>The client has Molluscum Contagiosum - Skin coloured pearly white papules with central umbilication. Most commonly seen on face and trunk in children.</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE24</t>
+  </si>
+  <si>
+    <t>Warts - Papules or nodules with a rough (Verrucous) surface</t>
+  </si>
+  <si>
+    <t>The client has Warts - Papules or nodules with a rough (Verrucous) surface</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE25</t>
+  </si>
+  <si>
+    <t>Seborrhea - Greasy scales and redness on central face and body folds</t>
+  </si>
+  <si>
+    <t>The client has Seborrhea - Greasy scales and redness on central face and body folds</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE26</t>
+  </si>
+  <si>
+    <t>Fixed Drug Reactions - Generalised red, wide spread with small bumps or blisters; or one or more dark skin areas</t>
+  </si>
+  <si>
+    <t>The client has Fixed Drug Reactions - Generalised red, wide spread with small bumps or blisters; or one or more dark skin areas</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE27</t>
+  </si>
+  <si>
+    <t>Eczema - Wet oozing sores or excoriated, thick patches</t>
+  </si>
+  <si>
+    <t>The client has Eczema - Wet oozing sores or excoriated, thick patches</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE28</t>
+  </si>
+  <si>
+    <t>Steven Johnson Syndrome - Severe reaction due to cotrimoxazole or NVP involving the skin as well as the eyes and the mouth.  Might cause difficulty in breathing</t>
+  </si>
+  <si>
+    <t>The client has Steven Johnson Syndrome - Severe reaction due to cotrimoxazole or NVP involving the skin as well as the eyes and the mouth.  Might cause difficulty in breathing</t>
+  </si>
+  <si>
+    <t>EmCare.B13S2.DE04</t>
+  </si>
+  <si>
+    <t>The client has had pus draining from the ear for less than 14 days</t>
+  </si>
+  <si>
+    <t>EmCare.B13S2.DE05</t>
+  </si>
+  <si>
+    <t>The client has had pus draining from the ear for 14 days or more</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE06</t>
+  </si>
+  <si>
+    <t>Generalised Skin Problem</t>
+  </si>
+  <si>
+    <t>The client has a generalised skin problem</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE07</t>
+  </si>
+  <si>
+    <t>Localised Skin Problem</t>
+  </si>
+  <si>
+    <t>The client has a localised skin problem</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE10</t>
+  </si>
+  <si>
+    <t>Possible Serious Abscess - Hot Tender Swelling</t>
+  </si>
+  <si>
+    <t>The client has a possible serious abscess - Hot tender swelling</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE11</t>
+  </si>
+  <si>
+    <t>Cellulitis - Red Tender Skin</t>
+  </si>
+  <si>
+    <t>The client has Cellulitis - Red tender skin</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE12</t>
+  </si>
+  <si>
+    <t>Papular Itching Rash(Prurigo) - Itching rash with small papules and scratch marks. Dark spots with pale centre</t>
+  </si>
+  <si>
+    <t>The client has Papular Itching Rash(Prurigo) - itching rash with small papules and scratch marks. Dark spots with pale centre</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE13</t>
+  </si>
+  <si>
+    <t>Ringworm (Tinea) - An itchy circular lesion with a raised edge and fine scaly area in the centre with loss of hair.  May also be found on body or web on feet</t>
+  </si>
+  <si>
+    <t>The client has Ringworm (Tinea) - An itchy circular lesion with a raised edge and fine scaly area in the centre with loss of hair.  May also be found on body or web on feet</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE14</t>
+  </si>
+  <si>
+    <t>Scabies - Rash and excoriations on torso; burrows in web space and wrists, face spared</t>
+  </si>
+  <si>
+    <t>The client has Scabies - Rash and excoriations on torso; burrows in web space and wrists, face spared</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE15</t>
+  </si>
+  <si>
+    <t>Chickenpox - Vesicles over body.  Vesicles appear progressively over days and form scabs after they rupture</t>
+  </si>
+  <si>
+    <t>The client has Chickenpox - Vesicles over body.  Vesicles appear progressively over days and form scabs after they rupture</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE16</t>
+  </si>
+  <si>
+    <t>Herpes Zoster -  Vesicles in one area on one side of body with intense pain or scars plus shooting pain.  Uncommon in children except where they are immuno-compromised (e.g. if infected with HIV)</t>
+  </si>
+  <si>
+    <t>The client has Herpes Zoster -  Vesicles in one area on one side of body with intense pain or scars plus shooting pain.  Uncommon in children except where they are immuno-compromised (e.g. if infected with HIV)</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE17</t>
+  </si>
+  <si>
+    <t>Impetigo / Folliculitis - Red, Tender, Warm Crusts or Small lesions</t>
+  </si>
+  <si>
+    <t>The client has Impetigo / Folliculitis - Red, Tender, Warm Crusts or Small lesions</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE32</t>
+  </si>
+  <si>
+    <t>Oral Thrush</t>
+  </si>
+  <si>
+    <t>The client has oral thrush</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE33</t>
+  </si>
+  <si>
+    <t>Mouth Sores or Mouth Ulcers - Deep and Extensive</t>
+  </si>
+  <si>
+    <t>The client has mouth sores or mouth ulcers that are deep and extensive</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE34</t>
+  </si>
+  <si>
+    <t>Mouth Sores or Mouth Ulcers - Not Deep and Extensive</t>
+  </si>
+  <si>
+    <t>The client has mouth sores or mouth ulcers that are not deep and extensive</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE36</t>
+  </si>
+  <si>
+    <t>The health care worker would like to add a skin problem</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE37</t>
+  </si>
+  <si>
+    <t>The health care worker would like to add an Oral Sores or Mouth Ulcers problem</t>
+  </si>
+  <si>
+    <t>EmCare.B14S2.DE38</t>
+  </si>
+  <si>
+    <t>The health care worker would like to add an Eye problem</t>
+  </si>
+  <si>
+    <t>EmCare.B15S2.DE01</t>
+  </si>
+  <si>
+    <t>Palmar Pallor</t>
+  </si>
+  <si>
+    <t>The client has palmar pallor</t>
+  </si>
+  <si>
+    <t>EmCare.B15S2.DE03</t>
+  </si>
+  <si>
+    <t>Some Palmar Pallor</t>
+  </si>
+  <si>
+    <t>The client has some palmar pallor</t>
+  </si>
+  <si>
+    <t>EmCare.B15S2.DE04</t>
+  </si>
+  <si>
+    <t>No Palmar Pallor</t>
+  </si>
+  <si>
+    <t>The client has no palmar pallor</t>
+  </si>
+  <si>
+    <t>EmCare.B15S2.DE06</t>
+  </si>
+  <si>
+    <t>EmCare.B15S2.DE07</t>
+  </si>
+  <si>
+    <t>EmCare.B15S2.DE08</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +2366,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D234"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1143,7 +2394,7 @@
         <v>42</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -1151,13 +2402,13 @@
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -1165,13 +2416,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -1179,13 +2430,13 @@
         <v>40</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -1193,13 +2444,13 @@
         <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -1207,13 +2458,13 @@
         <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -1221,13 +2472,13 @@
         <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -1235,13 +2486,13 @@
         <v>40</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -1249,13 +2500,13 @@
         <v>40</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -1263,13 +2514,13 @@
         <v>40</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12">
@@ -1277,13 +2528,13 @@
         <v>40</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -1291,13 +2542,13 @@
         <v>40</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14">
@@ -1305,13 +2556,13 @@
         <v>40</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1319,13 +2570,13 @@
         <v>40</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1333,13 +2584,13 @@
         <v>40</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
@@ -1347,13 +2598,13 @@
         <v>40</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -1361,13 +2612,13 @@
         <v>40</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -1375,13 +2626,13 @@
         <v>40</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -1389,13 +2640,13 @@
         <v>40</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21">
@@ -1403,13 +2654,13 @@
         <v>40</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>86</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22">
@@ -1417,13 +2668,13 @@
         <v>40</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>88</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23">
@@ -1431,13 +2682,13 @@
         <v>40</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24">
@@ -1445,13 +2696,13 @@
         <v>40</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25">
@@ -1459,13 +2710,13 @@
         <v>40</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26">
@@ -1473,13 +2724,13 @@
         <v>40</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27">
@@ -1487,13 +2738,13 @@
         <v>40</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28">
@@ -1501,13 +2752,13 @@
         <v>40</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29">
@@ -1515,13 +2766,13 @@
         <v>40</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30">
@@ -1529,13 +2780,13 @@
         <v>40</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31">
@@ -1543,13 +2794,13 @@
         <v>40</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>112</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
@@ -1557,13 +2808,13 @@
         <v>40</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33">
@@ -1571,13 +2822,13 @@
         <v>40</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34">
@@ -1585,13 +2836,13 @@
         <v>40</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35">
@@ -1599,13 +2850,13 @@
         <v>40</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>120</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36">
@@ -1613,13 +2864,13 @@
         <v>40</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>122</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37">
@@ -1627,13 +2878,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38">
@@ -1641,13 +2892,13 @@
         <v>40</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>126</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39">
@@ -1655,13 +2906,13 @@
         <v>40</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>128</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40">
@@ -1669,13 +2920,13 @@
         <v>40</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>130</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41">
@@ -1683,13 +2934,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>132</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42">
@@ -1697,13 +2948,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>134</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43">
@@ -1711,13 +2962,13 @@
         <v>40</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>136</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44">
@@ -1725,13 +2976,13 @@
         <v>40</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45">
@@ -1739,13 +2990,13 @@
         <v>40</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>140</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46">
@@ -1753,13 +3004,13 @@
         <v>40</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>142</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47">
@@ -1767,13 +3018,13 @@
         <v>40</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>144</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48">
@@ -1781,13 +3032,13 @@
         <v>40</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>146</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49">
@@ -1795,13 +3046,13 @@
         <v>40</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>149</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50">
@@ -1809,13 +3060,13 @@
         <v>40</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>152</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51">
@@ -1823,13 +3074,13 @@
         <v>40</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>154</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52">
@@ -1837,13 +3088,13 @@
         <v>40</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>157</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53">
@@ -1851,13 +3102,13 @@
         <v>40</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54">
@@ -1865,13 +3116,13 @@
         <v>40</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>163</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55">
@@ -1879,13 +3130,13 @@
         <v>40</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>165</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56">
@@ -1893,13 +3144,13 @@
         <v>40</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>167</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57">
@@ -1907,13 +3158,13 @@
         <v>40</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>170</v>
+        <v>204</v>
       </c>
     </row>
     <row r="58">
@@ -1921,13 +3172,13 @@
         <v>40</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>173</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59">
@@ -1935,13 +3186,13 @@
         <v>40</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>175</v>
+        <v>210</v>
       </c>
     </row>
     <row r="60">
@@ -1949,13 +3200,13 @@
         <v>40</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>177</v>
+        <v>213</v>
       </c>
     </row>
     <row r="61">
@@ -1963,13 +3214,13 @@
         <v>40</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>179</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62">
@@ -1977,13 +3228,13 @@
         <v>40</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>181</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63">
@@ -1991,13 +3242,13 @@
         <v>40</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>183</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64">
@@ -2005,13 +3256,13 @@
         <v>40</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>185</v>
+        <v>225</v>
       </c>
     </row>
     <row r="65">
@@ -2019,13 +3270,13 @@
         <v>40</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>186</v>
+        <v>226</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>187</v>
+        <v>227</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>187</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66">
@@ -2033,13 +3284,13 @@
         <v>40</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>189</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67">
@@ -2047,13 +3298,13 @@
         <v>40</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>191</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68">
@@ -2061,13 +3312,13 @@
         <v>40</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>193</v>
+        <v>237</v>
       </c>
     </row>
     <row r="69">
@@ -2075,13 +3326,13 @@
         <v>40</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>195</v>
+        <v>239</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>195</v>
+        <v>240</v>
       </c>
     </row>
     <row r="70">
@@ -2089,13 +3340,13 @@
         <v>40</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>197</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71">
@@ -2103,13 +3354,13 @@
         <v>40</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>199</v>
+        <v>222</v>
       </c>
     </row>
     <row r="72">
@@ -2117,13 +3368,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>200</v>
+        <v>245</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>201</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73">
@@ -2131,13 +3382,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>202</v>
+        <v>246</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>203</v>
+        <v>247</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>203</v>
+        <v>248</v>
       </c>
     </row>
     <row r="74">
@@ -2145,13 +3396,13 @@
         <v>40</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>205</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75">
@@ -2159,13 +3410,13 @@
         <v>40</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>206</v>
+        <v>252</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>207</v>
+        <v>253</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>207</v>
+        <v>254</v>
       </c>
     </row>
     <row r="76">
@@ -2173,13 +3424,13 @@
         <v>40</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>209</v>
+        <v>257</v>
       </c>
     </row>
     <row r="77">
@@ -2187,13 +3438,13 @@
         <v>40</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>210</v>
+        <v>258</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>211</v>
+        <v>259</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>211</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78">
@@ -2201,13 +3452,13 @@
         <v>40</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>213</v>
+        <v>263</v>
       </c>
     </row>
     <row r="79">
@@ -2215,13 +3466,13 @@
         <v>40</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>214</v>
+        <v>264</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>215</v>
+        <v>265</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>215</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80">
@@ -2229,13 +3480,13 @@
         <v>40</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>217</v>
+        <v>268</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>217</v>
+        <v>269</v>
       </c>
     </row>
     <row r="81">
@@ -2243,13 +3494,13 @@
         <v>40</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>220</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82">
@@ -2257,13 +3508,13 @@
         <v>40</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>222</v>
+        <v>275</v>
       </c>
     </row>
     <row r="83">
@@ -2271,13 +3522,13 @@
         <v>40</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>223</v>
+        <v>276</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>225</v>
+        <v>278</v>
       </c>
     </row>
     <row r="84">
@@ -2285,13 +3536,13 @@
         <v>40</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>227</v>
+        <v>280</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>228</v>
+        <v>281</v>
       </c>
     </row>
     <row r="85">
@@ -2299,13 +3550,13 @@
         <v>40</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>229</v>
+        <v>282</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>230</v>
+        <v>283</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>230</v>
+        <v>284</v>
       </c>
     </row>
     <row r="86">
@@ -2313,13 +3564,13 @@
         <v>40</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>231</v>
+        <v>285</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>232</v>
+        <v>286</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>232</v>
+        <v>287</v>
       </c>
     </row>
     <row r="87">
@@ -2327,13 +3578,13 @@
         <v>40</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>233</v>
+        <v>288</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>234</v>
+        <v>289</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>234</v>
+        <v>290</v>
       </c>
     </row>
     <row r="88">
@@ -2341,13 +3592,13 @@
         <v>40</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>235</v>
+        <v>291</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>236</v>
+        <v>292</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>236</v>
+        <v>293</v>
       </c>
     </row>
     <row r="89">
@@ -2355,13 +3606,13 @@
         <v>40</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>239</v>
+        <v>296</v>
       </c>
     </row>
     <row r="90">
@@ -2369,13 +3620,13 @@
         <v>40</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>241</v>
+        <v>298</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>242</v>
+        <v>299</v>
       </c>
     </row>
     <row r="91">
@@ -2383,13 +3634,13 @@
         <v>40</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>244</v>
+        <v>301</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>245</v>
+        <v>302</v>
       </c>
     </row>
     <row r="92">
@@ -2397,13 +3648,13 @@
         <v>40</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>246</v>
+        <v>303</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>247</v>
+        <v>304</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>247</v>
+        <v>305</v>
       </c>
     </row>
     <row r="93">
@@ -2411,13 +3662,13 @@
         <v>40</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>237</v>
+        <v>306</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>249</v>
+        <v>308</v>
       </c>
     </row>
     <row r="94">
@@ -2425,13 +3676,13 @@
         <v>40</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>252</v>
+        <v>311</v>
       </c>
     </row>
     <row r="95">
@@ -2439,13 +3690,13 @@
         <v>40</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>255</v>
+        <v>314</v>
       </c>
     </row>
     <row r="96">
@@ -2453,13 +3704,13 @@
         <v>40</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>257</v>
+        <v>93</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>258</v>
+        <v>316</v>
       </c>
     </row>
     <row r="97">
@@ -2467,13 +3718,13 @@
         <v>40</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>261</v>
+        <v>319</v>
       </c>
     </row>
     <row r="98">
@@ -2481,13 +3732,1917 @@
         <v>40</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>262</v>
+        <v>320</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>263</v>
+        <v>321</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>264</v>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="D99" t="s" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="D100" t="s" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="D101" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="D102" t="s" s="2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="D108" t="s" s="2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="D109" t="s" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="D110" t="s" s="2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="D112" t="s" s="2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="D113" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="D114" t="s" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="D115" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="D116" t="s" s="2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="D117" t="s" s="2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="D119" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="D120" t="s" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="D121" t="s" s="2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="D122" t="s" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="D123" t="s" s="2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="D124" t="s" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="D125" t="s" s="2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="D126" t="s" s="2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="D127" t="s" s="2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="D128" t="s" s="2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="D129" t="s" s="2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="D130" t="s" s="2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="D131" t="s" s="2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="D132" t="s" s="2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="D133" t="s" s="2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="D134" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="D135" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="D136" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="D137" t="s" s="2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="D138" t="s" s="2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="D139" t="s" s="2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D140" t="s" s="2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="D141" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="D142" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="D143" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="D144" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="D145" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C146" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="D146" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C147" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="D147" t="s" s="2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C148" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="D148" t="s" s="2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C149" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="D149" t="s" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="D150" t="s" s="2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C151" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="D151" t="s" s="2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="D152" t="s" s="2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C153" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="D153" t="s" s="2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="D154" t="s" s="2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C155" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="D155" t="s" s="2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C156" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="D156" t="s" s="2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C157" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="D157" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C158" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="D158" t="s" s="2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C159" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="D159" t="s" s="2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="D160" t="s" s="2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C161" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="D161" t="s" s="2">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C162" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="D162" t="s" s="2">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C163" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="D163" t="s" s="2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="D164" t="s" s="2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="D165" t="s" s="2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C166" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="D166" t="s" s="2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C167" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="D167" t="s" s="2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C168" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="D168" t="s" s="2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C169" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="D169" t="s" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C170" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="D170" t="s" s="2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C171" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="D171" t="s" s="2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C172" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="D172" t="s" s="2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C173" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="D173" t="s" s="2">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C174" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="D174" t="s" s="2">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C175" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="D175" t="s" s="2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C176" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="D176" t="s" s="2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C177" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="D177" t="s" s="2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C178" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="D178" t="s" s="2">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="D179" t="s" s="2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C180" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="D180" t="s" s="2">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C181" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="D181" t="s" s="2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C182" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="D182" t="s" s="2">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C183" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="D183" t="s" s="2">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C184" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="D184" t="s" s="2">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C185" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="D185" t="s" s="2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C186" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="D186" t="s" s="2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C187" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="D187" t="s" s="2">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C188" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="D188" t="s" s="2">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C189" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="D189" t="s" s="2">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C190" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="D190" t="s" s="2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="D191" t="s" s="2">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C192" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="D192" t="s" s="2">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C193" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="D193" t="s" s="2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C194" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="D194" t="s" s="2">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="D195" t="s" s="2">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C196" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="D196" t="s" s="2">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C197" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="D197" t="s" s="2">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C198" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="D198" t="s" s="2">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="D199" t="s" s="2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C200" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="D200" t="s" s="2">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="D201" t="s" s="2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C202" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="D202" t="s" s="2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C203" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="D203" t="s" s="2">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C204" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="D204" t="s" s="2">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="D205" t="s" s="2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C206" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="D206" t="s" s="2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C207" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="D207" t="s" s="2">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C208" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="D208" t="s" s="2">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C209" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="D209" t="s" s="2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C210" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="D210" t="s" s="2">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C211" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="D211" t="s" s="2">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C212" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="D212" t="s" s="2">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="C213" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="D213" t="s" s="2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C214" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="D214" t="s" s="2">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C215" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="D215" t="s" s="2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C216" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="D216" t="s" s="2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C217" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="D217" t="s" s="2">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C218" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="D218" t="s" s="2">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C219" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="D219" t="s" s="2">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="C220" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="D220" t="s" s="2">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="C221" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="D221" t="s" s="2">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C222" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="D222" t="s" s="2">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C223" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="D223" t="s" s="2">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C224" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="D224" t="s" s="2">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="C225" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="D225" t="s" s="2">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C226" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="D226" t="s" s="2">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C227" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="D227" t="s" s="2">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="C228" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="D228" t="s" s="2">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="C229" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="D229" t="s" s="2">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="C230" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="D230" t="s" s="2">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B231" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="C231" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="D231" t="s" s="2">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C232" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="D232" t="s" s="2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="C233" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="D233" t="s" s="2">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C234" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="D234" t="s" s="2">
+        <v>534</v>
       </c>
     </row>
   </sheetData>

--- a/CodeSystem-emc-custom-codes-codes.xlsx
+++ b/CodeSystem-emc-custom-codes-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-04-21T10:41:40+00:00</t>
+    <t>2022-05-02T16:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-emc-custom-codes-codes.xlsx
+++ b/CodeSystem-emc-custom-codes-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-02T16:42:45+00:00</t>
+    <t>2022-05-02T16:43:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
